--- a/artfynd/A 21710-2025 artfynd.xlsx
+++ b/artfynd/A 21710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129258453</v>
       </c>
       <c r="B2" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129258452</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21710-2025 artfynd.xlsx
+++ b/artfynd/A 21710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129258453</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129258452</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21710-2025 artfynd.xlsx
+++ b/artfynd/A 21710-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129258453</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129258452</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
